--- a/documentos/Cronograma_semanal Proyecto.xlsx
+++ b/documentos/Cronograma_semanal Proyecto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2203178-2609-4017-9365-505E0A10A8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF7D747-9867-48A0-ADAD-21BE6CAA59EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma semanal" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>CRONOGRAMA SEMANAL DE ACTIVIDADES</t>
   </si>
@@ -105,18 +105,6 @@
     <t>Resumen de la semana</t>
   </si>
   <si>
-    <t>Rol 1</t>
-  </si>
-  <si>
-    <t>Rol 2</t>
-  </si>
-  <si>
-    <t>Rol 3</t>
-  </si>
-  <si>
-    <t>Rol 4</t>
-  </si>
-  <si>
     <t>Escriba el nombre de cada rol en la columna A (reemplace 'Rol 1…4') y en cada día lo que realizó. Las fechas se toman de la semana indicada arriba.</t>
   </si>
   <si>
@@ -127,6 +115,57 @@
   </si>
   <si>
     <t>Github</t>
+  </si>
+  <si>
+    <t>Maria Tereza Salcedo</t>
+  </si>
+  <si>
+    <t>ADSO</t>
+  </si>
+  <si>
+    <t>Dizar Asociados</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>Se creo el inicio de sesion.</t>
+  </si>
+  <si>
+    <t>Se agrego funcionamiento en el inicio de sesion y que se registrar en la BD (MariaDB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Se comenzó a mejorar el diseño de alerta cuando algún campo está vacio</t>
+  </si>
+  <si>
+    <t>Se finalizo el diseño del alerta.</t>
+  </si>
+  <si>
+    <t>Se cambió los archivos que tenian .html por .php para que se conectaran con la base de datos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se organizo la rama principal de github (main). </t>
+  </si>
+  <si>
+    <t>Frontend (Erick, Sebastian)</t>
+  </si>
+  <si>
+    <t>Backend (Cristian, Keyner)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Cristian lider del proyecto</t>
+  </si>
+  <si>
+    <t>12:00pm-6:00pm</t>
+  </si>
+  <si>
+    <t>Documentador (Cristian, Sebastian)</t>
   </si>
 </sst>
 </file>
@@ -309,12 +348,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -327,27 +362,34 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -639,192 +681,232 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.453125" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="17" customWidth="1"/>
     <col min="3" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="29.08984375" customWidth="1"/>
-    <col min="9" max="9" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.140625" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="F3" s="3" t="s">
+      <c r="B3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="2">
         <v>46307</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="F4" s="3" t="s">
+      <c r="B4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="5">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3">
         <f>G3+4</f>
         <v>46311</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+    </row>
+    <row r="6" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8">
+      <c r="I8" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="6">
         <f>$G$3+0</f>
         <v>46307</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <f>$G$3+1</f>
         <v>46308</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <f>$G$3+2</f>
         <v>46309</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <f>$G$3+3</f>
         <v>46310</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="6">
         <f>$G$3+4</f>
         <v>46311</v>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+      <c r="H9" s="6"/>
+      <c r="I9" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="6">
